--- a/public/templates/modele-import-ebay.xlsx
+++ b/public/templates/modele-import-ebay.xlsx
@@ -1,47 +1,307 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Import eBay" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Annonces" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Valeurs autorisées" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Instructions" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="91">
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Custom label (SKU)</t>
+  </si>
+  <si>
+    <t>Category ID</t>
+  </si>
+  <si>
+    <t>Category Name</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Subtitle</t>
+  </si>
+  <si>
+    <t>P:EAN</t>
+  </si>
+  <si>
+    <t>Start price</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Item photo URL</t>
+  </si>
+  <si>
+    <t>Condition ID</t>
+  </si>
+  <si>
+    <t>Condition description</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Postal code</t>
+  </si>
+  <si>
+    <t>Shipping profile name</t>
+  </si>
+  <si>
+    <t>Return profile name</t>
+  </si>
+  <si>
+    <t>Payment profile name</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>MPN</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Product type</t>
+  </si>
+  <si>
+    <t>Sold item name</t>
+  </si>
+  <si>
+    <t>Compatible brand</t>
+  </si>
+  <si>
+    <t>Compatible device</t>
+  </si>
+  <si>
+    <t>Compatible model number</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Unit quantity</t>
+  </si>
+  <si>
+    <t>Unit type</t>
+  </si>
+  <si>
+    <t>Item specifics</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Occasion</t>
+  </si>
+  <si>
+    <t>FixedPrice</t>
+  </si>
+  <si>
+    <t>GTC</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>75001</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>30 jours</t>
+  </si>
+  <si>
+    <t>eBay Payments</t>
+  </si>
+  <si>
+    <t>Unité</t>
+  </si>
+  <si>
+    <t>Condition label</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1000 — Neuf</t>
+  </si>
+  <si>
+    <t>Revise</t>
+  </si>
+  <si>
+    <t>Auction</t>
+  </si>
+  <si>
+    <t>Days_3</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>1500 — Neuf avec défauts</t>
+  </si>
+  <si>
+    <t>Relist</t>
+  </si>
+  <si>
+    <t>Days_5</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2000 — Reconditionné</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Days_7</t>
+  </si>
+  <si>
+    <t>LU</t>
+  </si>
+  <si>
+    <t>3000 — Occasion</t>
+  </si>
+  <si>
+    <t>Days_10</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>7000 — Pour pièces</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Colonne</t>
+  </si>
+  <si>
+    <t>Add = créer, Revise = modifier, Relist = remetre en vente, End = terminer.</t>
+  </si>
+  <si>
+    <t>Référence vendeur unique. Conservez les zéros (texte).</t>
+  </si>
+  <si>
+    <t>Facultatif. Si vide, SNOWOLF détecte la catégorie via eBay Taxonomy (EBAY_FR).</t>
+  </si>
+  <si>
+    <t>Nom de catégorie indicatif pour aider la détection automatique.</t>
+  </si>
+  <si>
+    <t>Titre eBay, max 80 caractères. Obligatoire.</t>
+  </si>
+  <si>
+    <t>Prix de vente en euros. Obligatoire, &gt; 0.</t>
+  </si>
+  <si>
+    <t>Quantité disponible (défaut 1).</t>
+  </si>
+  <si>
+    <t>URL publique d'image. Laisser vide si aucune URL réelle.</t>
+  </si>
+  <si>
+    <t>1000 Neuf, 1500 Neuf défauts, 2000 Reconditionné, 3000 Occasion, 7000 Pièces.</t>
+  </si>
+  <si>
+    <t>Description HTML ou texte de l'annonce.</t>
+  </si>
+  <si>
+    <t>Format Brand=Apple|MPN=xxx|Model=yyy. Fusionné avec les colonnes dédiées (priorité aux colonnes).</t>
+  </si>
+  <si>
+    <t>Code postal en texte pour conserver les zéros (ex. 01000).</t>
+  </si>
+  <si>
+    <t>Code EAN/GTIN en texte pour conserver les zéros.</t>
+  </si>
+  <si>
+    <t>Référence fabricant. Texte forcé.</t>
+  </si>
+  <si>
+    <t>Rappel</t>
+  </si>
+  <si>
+    <t>Category ID est facultatif. SNOWOLF détecte la catégorie via l'API eBay Taxonomy (EBAY_FR). Une ligne = une annonce. Aucune publication automatique.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,14 +324,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,232 +669,552 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="25" customWidth="1"/>
+    <col min="20" max="20" width="23" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="25" width="12" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="28" max="28" width="20" customWidth="1"/>
+    <col min="29" max="29" width="21" customWidth="1"/>
+    <col min="30" max="30" width="27" customWidth="1"/>
+    <col min="31" max="33" width="12" customWidth="1"/>
+    <col min="34" max="34" width="17" customWidth="1"/>
+    <col min="35" max="35" width="13" customWidth="1"/>
+    <col min="36" max="36" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Action</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Custom label (SKU)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Category ID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Category Name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Title</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Subtitle</v>
-      </c>
-      <c r="G1" t="str">
-        <v>P:EAN</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Start price</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Quantity</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Item photo URL</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Condition ID</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Condition description</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Format</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Duration</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Location</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Country</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Postal code</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Shipping profile name</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Return profile name</v>
-      </c>
-      <c r="U1" t="str">
-        <v>Payment profile name</v>
-      </c>
-      <c r="V1" t="str">
-        <v>Brand</v>
-      </c>
-      <c r="W1" t="str">
-        <v>Manufacturer</v>
-      </c>
-      <c r="X1" t="str">
-        <v>MPN</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>Model</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>Product type</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>Sold item name</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>Compatible brand</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>Compatible device</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>Compatible model number</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>Color</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>Material</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>Unit quantity</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>Unit type</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>Item specifics</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Add</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
+    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v>3000</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Occasion</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v>FixedPrice</v>
-      </c>
-      <c r="O2" t="str">
-        <v>GTC</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Paris</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>FR</v>
-      </c>
-      <c r="R2" t="str">
-        <v>75001</v>
-      </c>
-      <c r="S2" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="T2" t="str">
-        <v>30 jours</v>
-      </c>
-      <c r="U2" t="str">
-        <v>eBay Payments</v>
-      </c>
-      <c r="V2" t="str">
-        <v/>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
-      </c>
-      <c r="Z2" t="str">
-        <v/>
-      </c>
-      <c r="AA2" t="str">
-        <v/>
-      </c>
-      <c r="AB2" t="str">
-        <v/>
-      </c>
-      <c r="AC2" t="str">
-        <v/>
-      </c>
-      <c r="AD2" t="str">
-        <v/>
-      </c>
-      <c r="AE2" t="str">
-        <v/>
-      </c>
-      <c r="AF2" t="str">
-        <v/>
-      </c>
-      <c r="AG2" t="str">
-        <v/>
-      </c>
-      <c r="AH2" t="str">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" t="s">
+        <v>37</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AJ1"/>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valeur non autorisée" error="Choisissez une valeur de la liste." sqref="A2:A200">
+      <formula1>'Valeurs autorisées'!$A$2:$A$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valeur non autorisée" error="Choisissez une valeur de la liste." sqref="K2:K200">
+      <formula1>'Valeurs autorisées'!$E$2:$E$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valeur non autorisée" error="Choisissez une valeur de la liste." sqref="N2:N200">
+      <formula1>'Valeurs autorisées'!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valeur non autorisée" error="Choisissez une valeur de la liste." sqref="O2:O200">
+      <formula1>'Valeurs autorisées'!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valeur non autorisée" error="Choisissez une valeur de la liste." sqref="Q2:Q200">
+      <formula1>'Valeurs autorisées'!$D$2:$D$8</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="AI2" t="str">
-        <v>Unité</v>
-      </c>
-      <c r="AJ2" t="str">
-        <v/>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AJ2"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>